--- a/output/boxplot_dls_table.xlsx
+++ b/output/boxplot_dls_table.xlsx
@@ -1738,7 +1738,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>m2/cap</t>
+          <t>m²/cap</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>m²/cap</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>m2/cap</t>
+          <t>m²/cap</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>m2/cap</t>
+          <t>m²/cap</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>m2/capita</t>
+          <t>m²/cap</t>
         </is>
       </c>
       <c r="H33" t="n">
